--- a/artfynd/A 22705-2026 artfynd.xlsx
+++ b/artfynd/A 22705-2026 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134285050</v>
+        <v>134285078</v>
       </c>
       <c r="B3" t="n">
-        <v>80474</v>
+        <v>83208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506178</v>
+        <v>506210</v>
       </c>
       <c r="R3" t="n">
-        <v>7115404</v>
+        <v>7115332</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134285078</v>
+        <v>134285050</v>
       </c>
       <c r="B4" t="n">
-        <v>83208</v>
+        <v>80474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506210</v>
+        <v>506178</v>
       </c>
       <c r="R4" t="n">
-        <v>7115332</v>
+        <v>7115404</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134285031</v>
+        <v>134285058</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>91956</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506230</v>
+        <v>506198</v>
       </c>
       <c r="R8" t="n">
-        <v>7115338</v>
+        <v>7115362</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,11 +1347,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1378,10 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134285058</v>
+        <v>134285031</v>
       </c>
       <c r="B9" t="n">
-        <v>91956</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1408,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506198</v>
+        <v>506230</v>
       </c>
       <c r="R9" t="n">
-        <v>7115362</v>
+        <v>7115338</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,6 +1444,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1868,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134285026</v>
+        <v>134285044</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>80475</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,21 +1879,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506438</v>
+        <v>506244</v>
       </c>
       <c r="R14" t="n">
-        <v>7115469</v>
+        <v>7115345</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,11 +1939,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1970,10 +1965,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134285044</v>
+        <v>134285026</v>
       </c>
       <c r="B15" t="n">
-        <v>80475</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1981,21 +1976,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2005,10 +2000,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506244</v>
+        <v>506438</v>
       </c>
       <c r="R15" t="n">
-        <v>7115345</v>
+        <v>7115469</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,6 +2036,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2368,7 +2368,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134285043</v>
+        <v>134285042</v>
       </c>
       <c r="B19" t="n">
         <v>80475</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506383</v>
+        <v>506311</v>
       </c>
       <c r="R19" t="n">
-        <v>7115487</v>
+        <v>7115436</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134285032</v>
+        <v>134285043</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>80475</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,21 +2476,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506231</v>
+        <v>506383</v>
       </c>
       <c r="R20" t="n">
-        <v>7115358</v>
+        <v>7115487</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2536,11 +2536,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2567,10 +2562,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134285042</v>
+        <v>134285032</v>
       </c>
       <c r="B21" t="n">
-        <v>80475</v>
+        <v>57975</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,21 +2573,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2602,10 +2597,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506311</v>
+        <v>506231</v>
       </c>
       <c r="R21" t="n">
-        <v>7115436</v>
+        <v>7115358</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2638,6 +2633,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2868,10 +2868,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134285035</v>
+        <v>134285074</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2879,21 +2879,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506221</v>
+        <v>506196</v>
       </c>
       <c r="R24" t="n">
-        <v>7115352</v>
+        <v>7115365</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2939,11 +2939,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2970,10 +2965,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134285074</v>
+        <v>134285035</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2981,21 +2976,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +3000,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506196</v>
+        <v>506221</v>
       </c>
       <c r="R25" t="n">
-        <v>7115365</v>
+        <v>7115352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3041,6 +3036,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3906,10 +3906,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134285079</v>
+        <v>134285075</v>
       </c>
       <c r="B34" t="n">
-        <v>83208</v>
+        <v>79359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,21 +3917,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506132</v>
+        <v>506179</v>
       </c>
       <c r="R34" t="n">
-        <v>7115416</v>
+        <v>7115419</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4003,10 +4003,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134285025</v>
+        <v>134285079</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>83208</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4014,21 +4014,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4038,10 +4038,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506451</v>
+        <v>506132</v>
       </c>
       <c r="R35" t="n">
-        <v>7115507</v>
+        <v>7115416</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4074,11 +4074,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4105,10 +4100,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134285075</v>
+        <v>134285025</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4116,21 +4111,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4140,10 +4135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506179</v>
+        <v>506451</v>
       </c>
       <c r="R36" t="n">
-        <v>7115419</v>
+        <v>7115507</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4176,6 +4171,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,10 +4202,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134285057</v>
+        <v>134285023</v>
       </c>
       <c r="B37" t="n">
-        <v>91956</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4213,21 +4213,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506211</v>
+        <v>506490</v>
       </c>
       <c r="R37" t="n">
-        <v>7115332</v>
+        <v>7115532</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4273,6 +4273,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4299,10 +4304,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134285023</v>
+        <v>134285057</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>91956</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4310,21 +4315,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4334,10 +4339,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506490</v>
+        <v>506211</v>
       </c>
       <c r="R38" t="n">
-        <v>7115532</v>
+        <v>7115332</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4370,11 +4375,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 22705-2026 artfynd.xlsx
+++ b/artfynd/A 22705-2026 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134285078</v>
+        <v>134285050</v>
       </c>
       <c r="B3" t="n">
-        <v>83208</v>
+        <v>80481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506210</v>
+        <v>506178</v>
       </c>
       <c r="R3" t="n">
-        <v>7115332</v>
+        <v>7115404</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134285050</v>
+        <v>134285078</v>
       </c>
       <c r="B4" t="n">
-        <v>80474</v>
+        <v>83215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506178</v>
+        <v>506210</v>
       </c>
       <c r="R4" t="n">
-        <v>7115404</v>
+        <v>7115332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
         <v>134285018</v>
       </c>
       <c r="B5" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134285049</v>
+        <v>134285048</v>
       </c>
       <c r="B6" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506290</v>
+        <v>506383</v>
       </c>
       <c r="R6" t="n">
-        <v>7115435</v>
+        <v>7115487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134285048</v>
+        <v>134285049</v>
       </c>
       <c r="B7" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506383</v>
+        <v>506290</v>
       </c>
       <c r="R7" t="n">
-        <v>7115487</v>
+        <v>7115435</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134285058</v>
+        <v>134285031</v>
       </c>
       <c r="B8" t="n">
-        <v>91956</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1287,21 +1287,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506198</v>
+        <v>506230</v>
       </c>
       <c r="R8" t="n">
-        <v>7115362</v>
+        <v>7115338</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,6 +1347,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1373,10 +1378,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134285031</v>
+        <v>134285058</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>91963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1384,21 +1389,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1408,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506230</v>
+        <v>506198</v>
       </c>
       <c r="R9" t="n">
-        <v>7115338</v>
+        <v>7115362</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1444,11 +1449,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1478,7 +1478,7 @@
         <v>134285062</v>
       </c>
       <c r="B10" t="n">
-        <v>91974</v>
+        <v>91981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>134285073</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>134285046</v>
       </c>
       <c r="B13" t="n">
-        <v>79518</v>
+        <v>79525</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134285044</v>
+        <v>134285024</v>
       </c>
       <c r="B14" t="n">
-        <v>80475</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,21 +1879,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506244</v>
+        <v>506473</v>
       </c>
       <c r="R14" t="n">
-        <v>7115345</v>
+        <v>7115518</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,6 +1939,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1965,10 +1970,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134285026</v>
+        <v>134285044</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>80482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,21 +1981,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2000,10 +2005,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>506438</v>
+        <v>506244</v>
       </c>
       <c r="R15" t="n">
-        <v>7115469</v>
+        <v>7115345</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,11 +2041,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2067,7 +2067,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134285024</v>
+        <v>134285026</v>
       </c>
       <c r="B16" t="n">
         <v>57975</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506473</v>
+        <v>506438</v>
       </c>
       <c r="R16" t="n">
-        <v>7115518</v>
+        <v>7115469</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2274,7 +2274,7 @@
         <v>134285056</v>
       </c>
       <c r="B18" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134285042</v>
+        <v>134285043</v>
       </c>
       <c r="B19" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506311</v>
+        <v>506383</v>
       </c>
       <c r="R19" t="n">
-        <v>7115436</v>
+        <v>7115487</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,10 +2465,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134285043</v>
+        <v>134285040</v>
       </c>
       <c r="B20" t="n">
-        <v>80475</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2476,21 +2476,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2500,10 +2500,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506383</v>
+        <v>506444</v>
       </c>
       <c r="R20" t="n">
-        <v>7115487</v>
+        <v>7115532</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2536,6 +2536,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2664,10 +2669,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134285040</v>
+        <v>134285042</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>80482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2675,21 +2680,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2699,10 +2704,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506444</v>
+        <v>506311</v>
       </c>
       <c r="R22" t="n">
-        <v>7115532</v>
+        <v>7115436</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2735,11 +2740,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2868,10 +2868,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134285074</v>
+        <v>134285035</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2879,21 +2879,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506196</v>
+        <v>506221</v>
       </c>
       <c r="R24" t="n">
-        <v>7115365</v>
+        <v>7115352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2939,6 +2939,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2965,10 +2970,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134285035</v>
+        <v>134285074</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2976,21 +2981,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3000,10 +3005,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506221</v>
+        <v>506196</v>
       </c>
       <c r="R25" t="n">
-        <v>7115352</v>
+        <v>7115365</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3036,11 +3041,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3067,7 +3067,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134285022</v>
+        <v>134285027</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3095,37 +3095,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506532</v>
+        <v>506407</v>
       </c>
       <c r="R26" t="n">
-        <v>7115536</v>
+        <v>7115472</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,7 +3142,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3189,7 +3169,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134285027</v>
+        <v>134285022</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3217,17 +3197,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506407</v>
+        <v>506532</v>
       </c>
       <c r="R27" t="n">
-        <v>7115472</v>
+        <v>7115536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3294,7 +3294,7 @@
         <v>134285019</v>
       </c>
       <c r="B28" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134285021</v>
+        <v>134285020</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -3417,16 +3417,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506154</v>
+        <v>506520</v>
       </c>
       <c r="R29" t="n">
-        <v>7115443</v>
+        <v>7115524</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3463,7 +3471,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gammalt bohål ca 2,5 m upp i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3490,10 +3498,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134285041</v>
+        <v>134285021</v>
       </c>
       <c r="B30" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3501,16 +3509,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3525,10 +3533,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506192</v>
+        <v>506154</v>
       </c>
       <c r="R30" t="n">
-        <v>7115357</v>
+        <v>7115443</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3565,7 +3573,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3592,10 +3600,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134285020</v>
+        <v>134285041</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3603,16 +3611,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3621,24 +3629,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506520</v>
+        <v>506192</v>
       </c>
       <c r="R31" t="n">
-        <v>7115524</v>
+        <v>7115357</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 2,5 m upp i tajgagrantickerötad granhögstubbe</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3906,10 +3906,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134285075</v>
+        <v>134285023</v>
       </c>
       <c r="B34" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,21 +3917,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506179</v>
+        <v>506490</v>
       </c>
       <c r="R34" t="n">
-        <v>7115419</v>
+        <v>7115532</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3977,6 +3977,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4003,10 +4008,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134285079</v>
+        <v>134285075</v>
       </c>
       <c r="B35" t="n">
-        <v>83208</v>
+        <v>79366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4014,21 +4019,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4038,10 +4043,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506132</v>
+        <v>506179</v>
       </c>
       <c r="R35" t="n">
-        <v>7115416</v>
+        <v>7115419</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4100,10 +4105,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134285025</v>
+        <v>134285079</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>83215</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4111,21 +4116,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4135,10 +4140,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506451</v>
+        <v>506132</v>
       </c>
       <c r="R36" t="n">
-        <v>7115507</v>
+        <v>7115416</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4171,11 +4176,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,10 +4202,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134285023</v>
+        <v>134285057</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>91963</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4213,21 +4213,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506490</v>
+        <v>506211</v>
       </c>
       <c r="R37" t="n">
-        <v>7115532</v>
+        <v>7115332</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4273,11 +4273,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4304,10 +4299,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134285057</v>
+        <v>134285025</v>
       </c>
       <c r="B38" t="n">
-        <v>91956</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4315,21 +4310,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4339,10 +4334,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506211</v>
+        <v>506451</v>
       </c>
       <c r="R38" t="n">
-        <v>7115332</v>
+        <v>7115507</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4375,6 +4370,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4404,7 +4404,7 @@
         <v>134285076</v>
       </c>
       <c r="B39" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 22705-2026 artfynd.xlsx
+++ b/artfynd/A 22705-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89595847</v>
+        <v>134285056</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506243.9415640516</v>
+        <v>506313</v>
       </c>
       <c r="R2" t="n">
-        <v>7115331.895599891</v>
+        <v>7115455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,26 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134285050</v>
+        <v>134285057</v>
       </c>
       <c r="B3" t="n">
-        <v>80481</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506178</v>
+        <v>506211</v>
       </c>
       <c r="R3" t="n">
-        <v>7115404</v>
+        <v>7115332</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134285078</v>
+        <v>134285058</v>
       </c>
       <c r="B4" t="n">
-        <v>83215</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506210</v>
+        <v>506198</v>
       </c>
       <c r="R4" t="n">
-        <v>7115332</v>
+        <v>7115362</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +969,7 @@
         <v>134285018</v>
       </c>
       <c r="B5" t="n">
-        <v>91967</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134285048</v>
+        <v>134285019</v>
       </c>
       <c r="B6" t="n">
-        <v>80481</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1093,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1117,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506383</v>
+        <v>506128</v>
       </c>
       <c r="R6" t="n">
-        <v>7115487</v>
+        <v>7115416</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134285049</v>
+        <v>134285062</v>
       </c>
       <c r="B7" t="n">
-        <v>80481</v>
+        <v>91988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1214,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506290</v>
+        <v>506243</v>
       </c>
       <c r="R7" t="n">
-        <v>7115435</v>
+        <v>7115368</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134285031</v>
+        <v>134285046</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>79532</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1311,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506230</v>
+        <v>506155</v>
       </c>
       <c r="R8" t="n">
-        <v>7115338</v>
+        <v>7115416</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1378,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134285058</v>
+        <v>134285078</v>
       </c>
       <c r="B9" t="n">
-        <v>91963</v>
+        <v>83222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1413,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506198</v>
+        <v>506210</v>
       </c>
       <c r="R9" t="n">
-        <v>7115362</v>
+        <v>7115332</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134285062</v>
+        <v>134285079</v>
       </c>
       <c r="B10" t="n">
-        <v>91981</v>
+        <v>83222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1510,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506243</v>
+        <v>506132</v>
       </c>
       <c r="R10" t="n">
-        <v>7115368</v>
+        <v>7115416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134285030</v>
+        <v>89595802</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>506318</v>
+        <v>506245</v>
       </c>
       <c r="R11" t="n">
-        <v>7115370</v>
+        <v>7115314</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1637,17 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1662,22 +1633,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134285073</v>
+        <v>89595847</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1685,21 +1660,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1709,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>506458</v>
+        <v>506244</v>
       </c>
       <c r="R12" t="n">
-        <v>7115472</v>
+        <v>7115332</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1739,12 +1714,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1759,44 +1734,48 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134285046</v>
+        <v>134285042</v>
       </c>
       <c r="B13" t="n">
-        <v>79525</v>
+        <v>80489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1806,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>506155</v>
+        <v>506311</v>
       </c>
       <c r="R13" t="n">
-        <v>7115416</v>
+        <v>7115436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1868,10 +1847,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134285024</v>
+        <v>134285043</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>80489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,21 +1858,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1903,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>506473</v>
+        <v>506383</v>
       </c>
       <c r="R14" t="n">
-        <v>7115518</v>
+        <v>7115487</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,11 +1918,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1973,7 +1947,7 @@
         <v>134285044</v>
       </c>
       <c r="B15" t="n">
-        <v>80482</v>
+        <v>80489</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,32 +2041,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134285026</v>
+        <v>89595849</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2102,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>506438</v>
+        <v>506251</v>
       </c>
       <c r="R16" t="n">
-        <v>7115469</v>
+        <v>7115303</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2132,17 +2106,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2157,44 +2126,48 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134285033</v>
+        <v>134285073</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2204,10 +2177,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>506227</v>
+        <v>506458</v>
       </c>
       <c r="R17" t="n">
-        <v>7115364</v>
+        <v>7115472</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,11 +2213,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2271,32 +2239,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134285056</v>
+        <v>134285074</v>
       </c>
       <c r="B18" t="n">
-        <v>91963</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2306,10 +2274,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>506313</v>
+        <v>506196</v>
       </c>
       <c r="R18" t="n">
-        <v>7115455</v>
+        <v>7115365</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2368,32 +2336,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134285043</v>
+        <v>134285075</v>
       </c>
       <c r="B19" t="n">
-        <v>80482</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2403,10 +2371,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>506383</v>
+        <v>506179</v>
       </c>
       <c r="R19" t="n">
-        <v>7115487</v>
+        <v>7115419</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,32 +2433,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134285040</v>
+        <v>134285076</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2500,10 +2468,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>506444</v>
+        <v>506154</v>
       </c>
       <c r="R20" t="n">
-        <v>7115532</v>
+        <v>7115412</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2536,11 +2504,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2567,10 +2530,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134285032</v>
+        <v>134285048</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,21 +2541,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2602,10 +2565,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>506231</v>
+        <v>506383</v>
       </c>
       <c r="R21" t="n">
-        <v>7115358</v>
+        <v>7115487</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2638,11 +2601,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2669,10 +2627,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134285042</v>
+        <v>134285049</v>
       </c>
       <c r="B22" t="n">
-        <v>80482</v>
+        <v>80488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2680,21 +2638,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2704,10 +2662,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>506311</v>
+        <v>506290</v>
       </c>
       <c r="R22" t="n">
-        <v>7115436</v>
+        <v>7115435</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2766,10 +2724,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134285037</v>
+        <v>134285050</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2777,21 +2735,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2801,10 +2759,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>506153</v>
+        <v>506178</v>
       </c>
       <c r="R23" t="n">
-        <v>7115422</v>
+        <v>7115404</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2837,11 +2795,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2868,27 +2821,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134285035</v>
+        <v>89595613</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2903,10 +2856,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>506221</v>
+        <v>506648</v>
       </c>
       <c r="R24" t="n">
-        <v>7115352</v>
+        <v>7115557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2933,17 +2886,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2958,44 +2911,48 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134285074</v>
+        <v>134285040</v>
       </c>
       <c r="B25" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3005,10 +2962,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>506196</v>
+        <v>506444</v>
       </c>
       <c r="R25" t="n">
-        <v>7115365</v>
+        <v>7115532</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3041,6 +2998,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3067,27 +3029,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134285027</v>
+        <v>134285041</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3102,10 +3064,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>506407</v>
+        <v>506192</v>
       </c>
       <c r="R26" t="n">
-        <v>7115472</v>
+        <v>7115357</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3142,7 +3104,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3169,7 +3131,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134285022</v>
+        <v>134285020</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3197,37 +3159,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506532</v>
+        <v>506520</v>
       </c>
       <c r="R27" t="n">
-        <v>7115536</v>
+        <v>7115524</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3264,7 +3214,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Födosökande</t>
+          <t>Gammalt bohål ca 2,5 m upp i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3291,10 +3241,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134285019</v>
+        <v>134285021</v>
       </c>
       <c r="B28" t="n">
-        <v>91967</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,21 +3252,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3326,10 +3276,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>506128</v>
+        <v>506154</v>
       </c>
       <c r="R28" t="n">
-        <v>7115416</v>
+        <v>7115443</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3362,6 +3312,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3388,7 +3343,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134285020</v>
+        <v>134285022</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -3416,25 +3371,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Storhögen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506520</v>
+        <v>506532</v>
       </c>
       <c r="R29" t="n">
-        <v>7115524</v>
+        <v>7115536</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3471,7 +3438,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Gammalt bohål ca 2,5 m upp i tajgagrantickerötad granhögstubbe</t>
+          <t>Födosökande</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3498,7 +3465,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134285021</v>
+        <v>134285023</v>
       </c>
       <c r="B30" t="n">
         <v>57975</v>
@@ -3533,10 +3500,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506154</v>
+        <v>506490</v>
       </c>
       <c r="R30" t="n">
-        <v>7115443</v>
+        <v>7115532</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3573,7 +3540,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3600,10 +3567,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134285041</v>
+        <v>134285024</v>
       </c>
       <c r="B31" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3611,16 +3578,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3635,10 +3602,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>506192</v>
+        <v>506473</v>
       </c>
       <c r="R31" t="n">
-        <v>7115357</v>
+        <v>7115518</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3675,7 +3642,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3702,7 +3669,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134285036</v>
+        <v>134285025</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3737,10 +3704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>506206</v>
+        <v>506451</v>
       </c>
       <c r="R32" t="n">
-        <v>7115367</v>
+        <v>7115507</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3777,7 +3744,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3804,7 +3771,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134285028</v>
+        <v>134285026</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -3839,10 +3806,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>506312</v>
+        <v>506438</v>
       </c>
       <c r="R33" t="n">
-        <v>7115422</v>
+        <v>7115469</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3906,7 +3873,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134285023</v>
+        <v>134285027</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -3941,10 +3908,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>506490</v>
+        <v>506407</v>
       </c>
       <c r="R34" t="n">
-        <v>7115532</v>
+        <v>7115472</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4008,10 +3975,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134285075</v>
+        <v>134285028</v>
       </c>
       <c r="B35" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4019,21 +3986,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4043,10 +4010,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>506179</v>
+        <v>506312</v>
       </c>
       <c r="R35" t="n">
-        <v>7115419</v>
+        <v>7115422</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4079,6 +4046,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4105,10 +4077,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134285079</v>
+        <v>134285030</v>
       </c>
       <c r="B36" t="n">
-        <v>83215</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4116,21 +4088,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4140,10 +4112,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>506132</v>
+        <v>506318</v>
       </c>
       <c r="R36" t="n">
-        <v>7115416</v>
+        <v>7115370</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4176,6 +4148,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,10 +4179,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134285057</v>
+        <v>134285031</v>
       </c>
       <c r="B37" t="n">
-        <v>91963</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4213,21 +4190,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4237,10 +4214,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>506211</v>
+        <v>506230</v>
       </c>
       <c r="R37" t="n">
-        <v>7115332</v>
+        <v>7115338</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4273,6 +4250,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4299,7 +4281,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134285025</v>
+        <v>134285032</v>
       </c>
       <c r="B38" t="n">
         <v>57975</v>
@@ -4334,10 +4316,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>506451</v>
+        <v>506231</v>
       </c>
       <c r="R38" t="n">
-        <v>7115507</v>
+        <v>7115358</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4374,7 +4356,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4401,10 +4383,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134285076</v>
+        <v>134285033</v>
       </c>
       <c r="B39" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4412,21 +4394,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4436,10 +4418,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>506154</v>
+        <v>506227</v>
       </c>
       <c r="R39" t="n">
-        <v>7115412</v>
+        <v>7115364</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4474,6 +4456,11 @@
           <t>2026-06-04</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4495,6 +4482,312 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134285035</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>506221</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7115352</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134285036</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>506206</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7115367</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134285037</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>506153</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7115422</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22705-2026 artfynd.xlsx
+++ b/artfynd/A 22705-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3135,27 +3135,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134285021</v>
+        <v>89595613</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506154</v>
+        <v>506648</v>
       </c>
       <c r="R27" t="n">
-        <v>7115443</v>
+        <v>7115557</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3200,17 +3200,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2020-09-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3225,1565 +3225,15 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>134285022</v>
-      </c>
-      <c r="B28" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>506532</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7115536</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Födosökande</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>134285023</v>
-      </c>
-      <c r="B29" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>506490</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7115532</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>134285024</v>
-      </c>
-      <c r="B30" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>506473</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7115518</v>
-      </c>
-      <c r="S30" t="n">
-        <v>10</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>134285025</v>
-      </c>
-      <c r="B31" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>506451</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7115507</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>134285026</v>
-      </c>
-      <c r="B32" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>506438</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7115469</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>134285027</v>
-      </c>
-      <c r="B33" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>506407</v>
-      </c>
-      <c r="R33" t="n">
-        <v>7115472</v>
-      </c>
-      <c r="S33" t="n">
-        <v>10</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>134285028</v>
-      </c>
-      <c r="B34" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>506312</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7115422</v>
-      </c>
-      <c r="S34" t="n">
-        <v>10</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>134285030</v>
-      </c>
-      <c r="B35" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>506318</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7115370</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>134285031</v>
-      </c>
-      <c r="B36" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>506230</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7115338</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>134285032</v>
-      </c>
-      <c r="B37" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>506231</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7115358</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>134285033</v>
-      </c>
-      <c r="B38" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>506227</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7115364</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>134285035</v>
-      </c>
-      <c r="B39" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>506221</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7115352</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>134285036</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>506206</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7115367</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>134285037</v>
-      </c>
-      <c r="B41" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>506153</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7115422</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>89595613</v>
-      </c>
-      <c r="B42" t="n">
-        <v>57950</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Storhögen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>506648</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7115557</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2020-09-26</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr">
+      <c r="AY27" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 22705-2026 artfynd.xlsx
+++ b/artfynd/A 22705-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3135,27 +3135,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89595613</v>
+        <v>134285021</v>
       </c>
       <c r="B27" t="n">
-        <v>57950</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>506648</v>
+        <v>506154</v>
       </c>
       <c r="R27" t="n">
-        <v>7115557</v>
+        <v>7115443</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3200,17 +3200,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-09-26</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3225,15 +3225,1565 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134285022</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>506532</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7115536</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Födosökande</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134285023</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>506490</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7115532</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134285024</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>506473</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7115518</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134285025</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>506451</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7115507</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134285026</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>506438</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7115469</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134285027</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>506407</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7115472</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134285028</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>506312</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7115422</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134285030</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>506318</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7115370</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134285031</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>506230</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7115338</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134285032</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>506231</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7115358</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134285033</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>506227</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7115364</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134285035</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>506221</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7115352</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134285036</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>506206</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7115367</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134285037</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>506153</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7115422</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>89595613</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storhögen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>506648</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7115557</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2020-09-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr">
+      <c r="AY42" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>

--- a/artfynd/A 22705-2026 artfynd.xlsx
+++ b/artfynd/A 22705-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285056</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285057</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285058</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285018</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285019</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285062</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285046</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285078</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285079</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1646,6 +1696,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595802</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595847</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285042</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285043</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285044</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2139,6 +2214,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595849</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2236,6 +2316,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285073</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2333,6 +2418,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285074</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2430,6 +2520,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285075</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2527,6 +2622,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285076</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2624,6 +2724,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285048</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2721,6 +2826,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285049</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2818,6 +2928,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285050</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2920,6 +3035,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285040</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3022,6 +3142,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285041</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3132,6 +3257,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285020</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3234,6 +3364,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285021</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3356,6 +3491,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285022</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3458,6 +3598,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285023</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3560,6 +3705,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285024</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3662,6 +3812,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3764,6 +3919,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285026</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3866,6 +4026,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285027</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3968,6 +4133,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285028</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4070,6 +4240,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285030</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4172,6 +4347,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285031</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4274,6 +4454,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285032</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4376,6 +4561,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285033</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4478,6 +4668,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285035</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4580,6 +4775,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285036</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4682,6 +4882,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134285037</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4788,8 +4993,56 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89595613</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 22705-2026 artfynd.xlsx
+++ b/artfynd/A 22705-2026 artfynd.xlsx
@@ -3268,7 +3268,7 @@
         <v>134285021</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>134285022</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>134285023</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>134285024</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>134285025</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>134285026</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>134285027</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>134285028</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>134285030</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>134285031</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>134285032</v>
       </c>
       <c r="B37" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>134285033</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>134285035</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>134285036</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         <v>134285037</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
